--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EA9C07-8FEC-4424-9055-8BBC393516A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D4981D-4AA0-4D43-A1CE-109473FC2610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1452" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="960" windowWidth="21768" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
     <sheet name="AccountCreationData" sheetId="7" r:id="rId2"/>
-    <sheet name="ProductDetails" sheetId="4" r:id="rId3"/>
-    <sheet name="SearchProduct" sheetId="6" r:id="rId4"/>
+    <sheet name="SearchProduct" sheetId="6" r:id="rId3"/>
+    <sheet name="ProductDetails" sheetId="4" r:id="rId4"/>
+    <sheet name="Testcase" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
   <si>
     <t>Password</t>
   </si>
@@ -49,9 +50,6 @@
     <t>LastName</t>
   </si>
   <si>
-    <t>SetPassword</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -79,42 +77,9 @@
     <t>MobilePhone</t>
   </si>
   <si>
-    <t>Mrs</t>
-  </si>
-  <si>
-    <t>hgsdtyf</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1985</t>
-  </si>
-  <si>
-    <t>San</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>91436</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>8489875678</t>
-  </si>
-  <si>
-    <t>ABCDEF</t>
-  </si>
-  <si>
-    <t>newtest2@gmail.com</t>
-  </si>
-  <si>
     <t>thanhthoai13@gmail.com</t>
   </si>
   <si>
@@ -127,71 +92,203 @@
     <t>thoaideptrai@gmail.com</t>
   </si>
   <si>
-    <t>Ms</t>
-  </si>
-  <si>
-    <t>TestUser1</t>
-  </si>
-  <si>
-    <t>TestUser2</t>
-  </si>
-  <si>
-    <t>TestUser3</t>
-  </si>
-  <si>
-    <t>UserTest1</t>
-  </si>
-  <si>
-    <t>UserTest2</t>
-  </si>
-  <si>
-    <t>UserTest3</t>
-  </si>
-  <si>
-    <t>1995</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>Address1</t>
+  </si>
+  <si>
+    <t>Address2</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Newsletter</t>
+  </si>
+  <si>
+    <t>SpecialOffers</t>
+  </si>
+  <si>
+    <t>user_20260405_1901_a1@testmail.com</t>
+  </si>
+  <si>
+    <t>user_20260405_1902_b2@testmail.com</t>
+  </si>
+  <si>
+    <t>Le Thi Rieng</t>
+  </si>
+  <si>
+    <t>Tran Van A</t>
+  </si>
+  <si>
+    <t>Thoai</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Mrs.</t>
+  </si>
+  <si>
+    <t>555$$</t>
+  </si>
+  <si>
+    <t>132313asd</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>1921</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Le</t>
+  </si>
+  <si>
+    <t>Rieng</t>
+  </si>
+  <si>
+    <t>Tran</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>FPT</t>
+  </si>
+  <si>
+    <t>HTC</t>
+  </si>
+  <si>
+    <t>VTV</t>
+  </si>
+  <si>
+    <t>123 Le Loi, HCM</t>
+  </si>
+  <si>
+    <t>Viet Nam</t>
+  </si>
+  <si>
+    <t>482A  Nơ Trang Long</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>Sate1</t>
+  </si>
+  <si>
+    <t>Sate2</t>
+  </si>
+  <si>
+    <t>Sate3</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>700000</t>
+  </si>
+  <si>
+    <t>700001</t>
+  </si>
+  <si>
+    <t>700002</t>
+  </si>
+  <si>
+    <t>0901234568</t>
+  </si>
+  <si>
+    <t>0901234569</t>
+  </si>
+  <si>
+    <t>0901234570</t>
+  </si>
+  <si>
+    <t>Test Case 1: Register User</t>
+  </si>
+  <si>
+    <t>1. Launch browser</t>
+  </si>
+  <si>
+    <t>2. Navigate to url 'http://automationexercise.com'</t>
+  </si>
+  <si>
+    <t>3. Verify that home page is visible successfully</t>
+  </si>
+  <si>
+    <t>4. Click on 'Signup / Login' button</t>
+  </si>
+  <si>
+    <t>5. Verify 'New User Signup!' is visible</t>
+  </si>
+  <si>
+    <t>6. Enter name and email address</t>
+  </si>
+  <si>
+    <t>7. Click 'Signup' button</t>
+  </si>
+  <si>
+    <t>8. Verify that 'ENTER ACCOUNT INFORMATION' is visible</t>
+  </si>
+  <si>
+    <t>9. Fill details: Title, Name, Email, Password, Date of birth</t>
+  </si>
+  <si>
+    <t>10. Select checkbox 'Sign up for our newsletter!'</t>
+  </si>
+  <si>
+    <t>11. Select checkbox 'Receive special offers from our partners!'</t>
+  </si>
+  <si>
+    <t>12. Fill details: First name, Last name, Company, Address, Address2, Country, State, City, Zipcode, Mobile Number</t>
+  </si>
+  <si>
+    <t>13. Click 'Create Account button'</t>
+  </si>
+  <si>
+    <t>14. Verify that 'ACCOUNT CREATED!' is visible</t>
+  </si>
+  <si>
+    <t>15. Click 'Continue' button</t>
+  </si>
+  <si>
+    <t>16. Verify that 'Logged in as username' is visible</t>
+  </si>
+  <si>
+    <t>17. Click 'Delete Account' button</t>
+  </si>
+  <si>
+    <t>18. Verify that 'ACCOUNT DELETED!' is visible and click 'Continue' button</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>Address2</t>
-  </si>
-  <si>
-    <t>EDFG1233</t>
-  </si>
-  <si>
-    <t>avc</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>asdasd</t>
-  </si>
-  <si>
-    <t>newt1231est31231311@gmail.com</t>
-  </si>
-  <si>
-    <t>newtest3123123133@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,16 +311,60 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -246,6 +387,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -254,13 +406,26 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -586,10 +751,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -600,13 +765,13 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1">
         <v>123</v>
@@ -626,39 +791,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
+    <col min="14" max="14" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="D1" s="2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>8</v>
@@ -669,195 +837,245 @@
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="O4" s="5" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>27</v>
+        <v>55</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{588956E5-EE1F-4BB2-B2C1-5B4CD1886FCA}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{956B82FE-7209-4C7E-A77C-4D1EFFCDE8FE}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{C541249B-1AD1-4CCB-8DBD-E68C3BDA767D}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -875,7 +1093,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -883,22 +1101,116 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A2"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19CBBA6-275A-4CE5-BBC4-47BBCE682D4F}">
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="44.6640625" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
+    <row r="1" spans="1:1" s="8" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="45" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" location="collapse1" display="https://automationexercise.com/test_cases - collapse1" xr:uid="{F4CA735A-56AB-49DE-B228-7F12EA758942}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://automationexercise.com/" xr:uid="{41DA66A2-7A5C-49AC-AD64-111569E6E38D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FFBFDF-1468-429D-97E8-DD429B2D1737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC9162B-EA27-4EBA-9343-F1676C2C71D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="852" windowWidth="21768" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="2148" windowWidth="23040" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
     <sheet name="AccountCreationData" sheetId="7" r:id="rId2"/>
-    <sheet name="SearchProduct" sheetId="6" r:id="rId3"/>
-    <sheet name="ProductDetails" sheetId="4" r:id="rId4"/>
-    <sheet name="Testcase" sheetId="8" r:id="rId5"/>
+    <sheet name="ContactUsForm" sheetId="10" r:id="rId3"/>
+    <sheet name="SearchProduct" sheetId="6" r:id="rId4"/>
+    <sheet name="ProductDetails" sheetId="4" r:id="rId5"/>
+    <sheet name="Testcase" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="86">
   <si>
     <t>Password</t>
   </si>
@@ -240,13 +241,55 @@
   </si>
   <si>
     <t>https://automationexercise.com/test_cases#collapse1</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>File chosen</t>
+  </si>
+  <si>
+    <t>Bugs</t>
+  </si>
+  <si>
+    <t>Quần áo không có</t>
+  </si>
+  <si>
+    <t>132313asdsadasdsd  dasdasdasda</t>
+  </si>
+  <si>
+    <t>123@@ asdasdasds  as dasd</t>
+  </si>
+  <si>
+    <t>555$$  xcvxcbxc  zvzxvtqw yw qw</t>
+  </si>
+  <si>
+    <t>src/test/resources/TestData/TestData.xlsx</t>
+  </si>
+  <si>
+    <t>Logo/logo.jpg</t>
+  </si>
+  <si>
+    <t>README.md</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>white</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +327,29 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -299,7 +365,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -333,6 +399,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -341,7 +444,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -352,6 +455,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1056,8 +1164,103 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE416EC-5D80-4FBD-B182-45BC7F47C371}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="mailto:thanhthoai13@gmail.com" xr:uid="{F5905F75-CDF5-4DF3-BC43-A66695232A19}"/>
+    <hyperlink ref="B3" r:id="rId2" display="mailto:user_20260405_1901_a1@testmail.com" xr:uid="{7C3C90A1-C5D4-4CF6-9FDB-AE703DB03895}"/>
+    <hyperlink ref="B4" r:id="rId3" display="mailto:user_20260405_1902_b2@testmail.com" xr:uid="{65ADCFB1-AC13-4F5E-B175-68839E6CE372}"/>
+    <hyperlink ref="B5" r:id="rId4" display="mailto:thanhthoai13@gmail.com" xr:uid="{2122D26E-85D8-4101-8672-8A6469D437BE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -1070,12 +1273,27 @@
         <v>4</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1101,7 +1319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19CBBA6-275A-4CE5-BBC4-47BBCE682D4F}">
   <dimension ref="F1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74796E8A-6939-4679-BE8B-E7560C4C7B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B851B0-F329-45EA-BDEB-03F430FFE706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="2148" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="94">
   <si>
     <t>Password</t>
   </si>
@@ -87,9 +87,6 @@
     <t>thanh@gmail.com</t>
   </si>
   <si>
-    <t>thoaideptrai@gmail.com</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>user_20260405_1901_a1@testmail.com</t>
   </si>
   <si>
-    <t>user_20260405_1902_b2@testmail.com</t>
-  </si>
-  <si>
     <t>Le Thi Rieng</t>
   </si>
   <si>
@@ -261,30 +255,18 @@
     <t>123@@ asdasdasds  as dasd</t>
   </si>
   <si>
-    <t>555$$  xcvxcbxc  zvzxvtqw yw qw</t>
-  </si>
-  <si>
     <t>src/test/resources/TestData/TestData.xlsx</t>
   </si>
   <si>
     <t>Logo/logo.jpg</t>
   </si>
   <si>
-    <t>README.md</t>
-  </si>
-  <si>
     <t>abc</t>
   </si>
   <si>
     <t>pink</t>
   </si>
   <si>
-    <t>white</t>
-  </si>
-  <si>
-    <t>user_20260w402225_1901_a1@testmail.com</t>
-  </si>
-  <si>
     <t>Review</t>
   </si>
   <si>
@@ -294,9 +276,6 @@
     <t>Joend</t>
   </si>
   <si>
-    <t>Lara</t>
-  </si>
-  <si>
     <t>thanthaod22@gmail.com</t>
   </si>
   <si>
@@ -307,6 +286,41 @@
   </si>
   <si>
     <t>Xấu quá</t>
+  </si>
+  <si>
+    <t>Ngày hôm nay trời trong xanh
+Đẹp như tranh
+Mình cùng dạo vòng quanh cả thế giới
+Đừng vội nhanh
+Một hành trình nhật ký yêu thương đời mình
+Hát vu vơ về tình đầu em ơi
+Ngày hôm ấy là cô bé tuổi đôi mươi
+Vậy mà giờ đã lớn trưởng thành hơn</t>
+  </si>
+  <si>
+    <t>j97@gmail.com</t>
+  </si>
+  <si>
+    <t>J97</t>
+  </si>
+  <si>
+    <t>user_20www5_1901_a1@testmail.com</t>
+  </si>
+  <si>
+    <t>user_2026eqs5_1901_a1@testmail.com</t>
+  </si>
+  <si>
+    <t>userzzz_20260405_1902_b2@testmail.com</t>
+  </si>
+  <si>
+    <t>Những vụn vỡ đã lỡ đêm lại nhớ
+Nằm mơ gọi tên em
+Thiên lý ơi
+Em có thể ở lại đây không
+Biết chăng ngoài trời mưa giông
+Nhiều cô đơn lắm em
+Thiên lý ơi
+Anh chỉ mong người bình yên thôi</t>
   </si>
 </sst>
 </file>
@@ -468,7 +482,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -485,6 +499,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -808,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -819,18 +840,18 @@
         <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1">
         <v>1231232131231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -841,30 +862,23 @@
         <v>222</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1">
-        <v>123133122</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="A5" s="14"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="B2" r:id="rId2" display="admin@123" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="A4" r:id="rId3" xr:uid="{509E6746-0179-4762-9083-E75C9AF220D4}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{E98AE939-4CA4-41CC-B36A-1121D2CA0B99}"/>
-    <hyperlink ref="A3" r:id="rId5" xr:uid="{CF8D4D16-E15E-4657-8DBB-F708AE9F7CBF}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{CF8D4D16-E15E-4657-8DBB-F708AE9F7CBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId6"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -880,43 +894,47 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="B4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="13"/>
@@ -937,6 +955,7 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00F61BF3-783A-4981-8854-FD11F801CCC7}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{42328E72-1380-4872-B2D4-87434DCCC719}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{B86B6138-3464-419A-BA1E-F2295DBB2982}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -944,7 +963,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -973,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>4</v>
@@ -991,10 +1010,10 @@
         <v>9</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>5</v>
@@ -1006,10 +1025,10 @@
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
@@ -1029,61 +1048,61 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="Q2" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1091,221 +1110,168 @@
         <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="O3" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="L4" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="Q4" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="M5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="R5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="S5" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1313,105 +1279,99 @@
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{588956E5-EE1F-4BB2-B2C1-5B4CD1886FCA}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{956B82FE-7209-4C7E-A77C-4D1EFFCDE8FE}"/>
-    <hyperlink ref="A6" r:id="rId3" xr:uid="{C541249B-1AD1-4CCB-8DBD-E68C3BDA767D}"/>
-    <hyperlink ref="A3" r:id="rId4" xr:uid="{D2CEBA7D-1D9E-4A65-96C1-EA297B87A456}"/>
-    <hyperlink ref="A2" r:id="rId5" xr:uid="{A2606004-4F0F-4F89-884D-5EBAD941ACE6}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{D2CEBA7D-1D9E-4A65-96C1-EA297B87A456}"/>
+    <hyperlink ref="A2" r:id="rId4" xr:uid="{A2606004-4F0F-4F89-884D-5EBAD941ACE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE416EC-5D80-4FBD-B182-45BC7F47C371}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" customWidth="1"/>
+    <col min="4" max="4" width="53.6640625" customWidth="1"/>
+    <col min="5" max="5" width="44.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="B4" s="11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>93</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="mailto:thanhthoai13@gmail.com" xr:uid="{F5905F75-CDF5-4DF3-BC43-A66695232A19}"/>
     <hyperlink ref="B3" r:id="rId2" display="mailto:user_20260405_1901_a1@testmail.com" xr:uid="{7C3C90A1-C5D4-4CF6-9FDB-AE703DB03895}"/>
-    <hyperlink ref="B4" r:id="rId3" display="mailto:user_20260405_1902_b2@testmail.com" xr:uid="{65ADCFB1-AC13-4F5E-B175-68839E6CE372}"/>
-    <hyperlink ref="B5" r:id="rId4" display="mailto:thanhthoai13@gmail.com" xr:uid="{2122D26E-85D8-4101-8672-8A6469D437BE}"/>
+    <hyperlink ref="B4" r:id="rId3" display="mailto:thanhthoai13@gmail.com" xr:uid="{2122D26E-85D8-4101-8672-8A6469D437BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1419,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -1434,17 +1394,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1419,7 @@
     <row r="1" spans="6:6" s="7" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
